--- a/03_decision/2024.12.AMTM/02.credit.xlsx
+++ b/03_decision/2024.12.AMTM/02.credit.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\longh\Desktop\X\03_decision\2024.12.AMTM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7DC651B-917F-472A-8879-CD40CD5D6D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B0EDAFB-6742-4110-A5BE-F1DE79B6DAAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17304" windowHeight="16680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="from.scoping" sheetId="1" r:id="rId1"/>
+    <sheet name="risk_factors" sheetId="2" r:id="rId2"/>
+    <sheet name="peers.hand.pick" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="IQ_CH">110000</definedName>
@@ -62,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="133">
   <si>
     <t>CACI</t>
   </si>
@@ -293,13 +295,577 @@
   </si>
   <si>
     <t>84-4015419</t>
+  </si>
+  <si>
+    <t>Key Risks Related to Amentum's Business and Industry</t>
+  </si>
+  <si>
+    <r>
+      <t>Dependence on U.S. Federal Government Contracts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <t>A significant portion of revenues comes from U.S. federal contracts.</t>
+  </si>
+  <si>
+    <t>A reduction or cessation of these contracts would materially harm business and financial results.</t>
+  </si>
+  <si>
+    <r>
+      <t>Government Reviews and Audits</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <t>Contracts are subject to frequent audits, which could lead to delayed payments, legal actions, fines, or other penalties.</t>
+  </si>
+  <si>
+    <r>
+      <t>Federal Budget Uncertainty</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <t>Delays in federal budget approval, spending cuts, or shifts in priorities could negatively impact operations and revenues.</t>
+  </si>
+  <si>
+    <r>
+      <t>Intense Market Competition</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <t>High competition could result in loss of market share and adversely affect financial performance.</t>
+  </si>
+  <si>
+    <r>
+      <t>Reliance on New Contract Awards</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <t>Success depends on securing new contracts and their timely award.</t>
+  </si>
+  <si>
+    <r>
+      <t>Economic Risks</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <t>Inflation, high-interest rates, and cost increases could reduce demand for services and profitability, especially for fixed-price contracts.</t>
+  </si>
+  <si>
+    <r>
+      <t>Workplace Safety and Environmental Risks</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <t>Operations involve safety hazards, and accidents could result in financial losses, reputational harm, and legal liabilities.</t>
+  </si>
+  <si>
+    <r>
+      <t>Fixed-Price Contract Risks</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <t>Fixed-price contracts pose risks of cost overruns, potentially impacting profits.</t>
+  </si>
+  <si>
+    <r>
+      <t>Performance Issues</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <t>Failure to meet contract requirements or schedules could harm financial outcomes and reputation.</t>
+  </si>
+  <si>
+    <r>
+      <t>Backlog Uncertainty</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <t>Contract backlog is not a guaranteed indicator of future revenue, as contracts can be adjusted, canceled, or suspended.</t>
+  </si>
+  <si>
+    <r>
+      <t>Regulatory and Liability Risks</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <t>Noncompliance with regulations or liabilities from operations could lead to monetary damages, inadequate insurance coverage, and reputational damage.</t>
+  </si>
+  <si>
+    <r>
+      <t>Reliance on Third Parties</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <t>Dependence on third parties for contract execution, misconduct, or regulatory noncompliance could reduce revenue and profitability.</t>
+  </si>
+  <si>
+    <r>
+      <t>Cybersecurity Risks</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <t>Cyber breaches or IT failures could disrupt operations and result in financial losses and reputational harm.</t>
+  </si>
+  <si>
+    <r>
+      <t>Nuclear Services Indemnification</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <t>Inadequate indemnification for nuclear services could negatively affect business operations and financial health.</t>
+  </si>
+  <si>
+    <t>Risks Related to International Operations</t>
+  </si>
+  <si>
+    <r>
+      <t>1. Political and Economic Instability</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: International operations face risks like unfavorable political developments and weak foreign economies.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. Regulatory and Tax Changes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Changes in domestic and international laws, tax policies, and outcomes of tax audits could harm profitability and reputation.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3. Security Risks</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Operating in high-risk international locations poses safety concerns for employees and could lead to unexpected costs.</t>
+    </r>
+  </si>
+  <si>
+    <t>Risks Related to Acquisitions, Investments, Joint Ventures, and Divestitures</t>
+  </si>
+  <si>
+    <r>
+      <t>1. Joint Ventures and Partnerships</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: These involve risks outside the company’s control, potentially affecting outcomes.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. Goodwill Impairment</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Impairment of goodwill or intangible assets could significantly impact financial results.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3. Acquisition Strategy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Dependence on acquisitions and investments to sustain growth introduces risks, including integration challenges and unforeseen costs.</t>
+    </r>
+  </si>
+  <si>
+    <t>Risks Related to Regulatory Compliance</t>
+  </si>
+  <si>
+    <r>
+      <t>1. Federal Contractor Regulations</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Non-compliance or changes in procurement laws and regulations could negatively impact the business.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. Data Privacy and Security</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Compliance with evolving data privacy laws may lead to investigations, penalties, or required operational changes.</t>
+    </r>
+  </si>
+  <si>
+    <t>Risks Related to Indebtedness and Credit Markets</t>
+  </si>
+  <si>
+    <r>
+      <t>1. Significant Debt Levels</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: High indebtedness limits financial flexibility and could affect operations.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. Variable Interest Rates</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Exposure to interest rate fluctuations increases financial vulnerability.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3. Restrictive Covenants</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Debt agreements may restrict business activities and operational flexibility.</t>
+    </r>
+  </si>
+  <si>
+    <t>Risks Related to the Transaction (Separation and Distribution with Jacobs)</t>
+  </si>
+  <si>
+    <r>
+      <t>1. Integration Challenges</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Anticipated financial benefits from the transaction may not materialize, and integration may be difficult.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. Tax Implications</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: If the transaction does not qualify as tax-free, Jacobs or its shareholders could face substantial tax liabilities.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3. Operational Restrictions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Restrictions to preserve tax treatment could hinder strategic initiatives.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>4. Transition Services Agreement</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Failure to have systems in place after the agreement's expiration could disrupt operations.</t>
+    </r>
+  </si>
+  <si>
+    <t>Risks Related to Common Stock</t>
+  </si>
+  <si>
+    <r>
+      <t>1. Equityholder Concentration</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Significant stock ownership by Amentum Equityholder could influence decisions.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. Stock Price Volatility</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Fluctuating quarterly results and large share sales could negatively affect the stock price.</t>
+    </r>
+  </si>
+  <si>
+    <t>Risks Related to Climate Change</t>
+  </si>
+  <si>
+    <r>
+      <t>1. Weather-Related Impacts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Climate-related events may damage equipment and infrastructure, harming operations.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. Market and Regulatory Responses</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Failure to meet climate-related commitments or regulatory demands could affect operations and reputation.</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -327,6 +893,20 @@
       <b/>
       <sz val="11"/>
       <color theme="1" tint="4.9989318521683403E-2"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -388,7 +968,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -416,6 +996,17 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -697,7 +1288,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="44.88671875" bestFit="1" customWidth="1"/>
@@ -1230,7 +1821,7 @@
         <v>271628265</v>
       </c>
     </row>
-    <row r="33" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C33" s="7" t="s">
         <v>76</v>
       </c>
@@ -1239,7 +1830,7 @@
         <v>844015419</v>
       </c>
     </row>
-    <row r="34" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C34" s="8" t="s">
         <v>73</v>
       </c>
@@ -1247,6 +1838,9 @@
         <f t="shared" si="0"/>
         <v>843981963</v>
       </c>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B37" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1254,4 +1848,366 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFA4B072-1546-469C-81C2-2BA1C35A95AD}">
+  <dimension ref="A1:B97"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="15" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B2" s="15" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B3" s="16"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B4" s="16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B5" s="16" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B7" s="15" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B8" s="16"/>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B9" s="16" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B11" s="15" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B12" s="16"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B13" s="16" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B15" s="15" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B16" s="16"/>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B17" s="16" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B19" s="15" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B20" s="16"/>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B21" s="16" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B23" s="15" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B24" s="16"/>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B25" s="16" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B27" s="15" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B28" s="16"/>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B29" s="16" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B31" s="15" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B32" s="16"/>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B33" s="16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B35" s="15" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B36" s="16"/>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B37" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B39" s="15" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B40" s="16"/>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B41" s="16" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B43" s="15" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B44" s="16"/>
+    </row>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B45" s="16" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B47" s="15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B48" s="16"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B49" s="16" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B51" s="15" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B52" s="16"/>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B53" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B55" s="15" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B56" s="16"/>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B57" s="16" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A59" s="17" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" s="16"/>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" s="18" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" s="18" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" s="18" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A65" s="17" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A66" s="16"/>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A67" s="18" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A68" s="18" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A69" s="18" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A71" s="17" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A72" s="16"/>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A73" s="18" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A74" s="18" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A76" s="17" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A77" s="16"/>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A78" s="18" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A79" s="18" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A80" s="18" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A82" s="17" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A83" s="16"/>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A84" s="18" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A85" s="18" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A86" s="18" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A87" s="18" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A89" s="17" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A90" s="16"/>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A91" s="18" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A92" s="18" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A94" s="17" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A95" s="16"/>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A96" s="18" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A97" s="18" t="s">
+        <v>132</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CACB33E-4510-4F0C-9DA0-AC4A31A9D7C3}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/03_decision/2024.12.AMTM/02.credit.xlsx
+++ b/03_decision/2024.12.AMTM/02.credit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\longh\Desktop\X\03_decision\2024.12.AMTM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B0EDAFB-6742-4110-A5BE-F1DE79B6DAAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70DDBC6F-6728-4B5D-8337-265F6DA05CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17304" windowHeight="16680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="from.scoping" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="134">
   <si>
     <t>CACI</t>
   </si>
@@ -859,6 +859,9 @@
       </rPr>
       <t>: Failure to meet climate-related commitments or regulatory demands could affect operations and reputation.</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">still didn't know how to take advantage of it. </t>
   </si>
 </sst>
 </file>
@@ -994,9 +997,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1007,6 +1007,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1317,10 +1320,10 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="13"/>
+      <c r="G3" s="18"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
@@ -1840,7 +1843,7 @@
       </c>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B37" s="14"/>
+      <c r="B37" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1856,345 +1859,345 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="14" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="14" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B3" s="16"/>
+      <c r="B3" s="15"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="15" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="15" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="14" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B8" s="16"/>
+      <c r="B8" s="15"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="15" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="14" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B12" s="16"/>
+      <c r="B12" s="15"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="15" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="14" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B16" s="16"/>
+      <c r="B16" s="15"/>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="15" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="14" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B20" s="16"/>
+      <c r="B20" s="15"/>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B21" s="16" t="s">
+      <c r="B21" s="15" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B24" s="16"/>
+      <c r="B24" s="15"/>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="15" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="14" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B28" s="16"/>
+      <c r="B28" s="15"/>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B29" s="16" t="s">
+      <c r="B29" s="15" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="31" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="14" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="32" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B32" s="16"/>
+      <c r="B32" s="15"/>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B33" s="16" t="s">
+      <c r="B33" s="15" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="35" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B35" s="15" t="s">
+      <c r="B35" s="14" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B36" s="16"/>
+      <c r="B36" s="15"/>
     </row>
     <row r="37" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B37" s="16" t="s">
+      <c r="B37" s="15" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="39" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B39" s="15" t="s">
+      <c r="B39" s="14" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="40" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B40" s="16"/>
+      <c r="B40" s="15"/>
     </row>
     <row r="41" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B41" s="16" t="s">
+      <c r="B41" s="15" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="43" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B43" s="15" t="s">
+      <c r="B43" s="14" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="44" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B44" s="16"/>
+      <c r="B44" s="15"/>
     </row>
     <row r="45" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B45" s="16" t="s">
+      <c r="B45" s="15" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="47" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B47" s="15" t="s">
+      <c r="B47" s="14" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="48" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B48" s="16"/>
+      <c r="B48" s="15"/>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B49" s="16" t="s">
+      <c r="B49" s="15" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B51" s="15" t="s">
+      <c r="B51" s="14" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B52" s="16"/>
+      <c r="B52" s="15"/>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B53" s="16" t="s">
+      <c r="B53" s="15" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B55" s="15" t="s">
+      <c r="B55" s="14" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B56" s="16"/>
+      <c r="B56" s="15"/>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B57" s="16" t="s">
+      <c r="B57" s="15" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="59" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="17" t="s">
+      <c r="A59" s="16" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A60" s="16"/>
+      <c r="A60" s="15"/>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A61" s="18" t="s">
+      <c r="A61" s="17" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A62" s="18" t="s">
+      <c r="A62" s="17" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A63" s="18" t="s">
+      <c r="A63" s="17" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="65" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A65" s="17" t="s">
+      <c r="A65" s="16" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A66" s="16"/>
+      <c r="A66" s="15"/>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A67" s="18" t="s">
+      <c r="A67" s="17" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A68" s="18" t="s">
+      <c r="A68" s="17" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A69" s="18" t="s">
+      <c r="A69" s="17" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="71" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A71" s="17" t="s">
+      <c r="A71" s="16" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A72" s="16"/>
+      <c r="A72" s="15"/>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A73" s="18" t="s">
+      <c r="A73" s="17" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A74" s="18" t="s">
+      <c r="A74" s="17" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="76" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A76" s="17" t="s">
+      <c r="A76" s="16" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A77" s="16"/>
+      <c r="A77" s="15"/>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A78" s="18" t="s">
+      <c r="A78" s="17" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A79" s="18" t="s">
+      <c r="A79" s="17" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A80" s="18" t="s">
+      <c r="A80" s="17" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="82" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A82" s="17" t="s">
+      <c r="A82" s="16" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A83" s="16"/>
+      <c r="A83" s="15"/>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A84" s="18" t="s">
+      <c r="A84" s="17" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A85" s="18" t="s">
+      <c r="A85" s="17" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A86" s="18" t="s">
+      <c r="A86" s="17" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A87" s="18" t="s">
+      <c r="A87" s="17" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="89" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A89" s="17" t="s">
+      <c r="A89" s="16" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A90" s="16"/>
+      <c r="A90" s="15"/>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A91" s="18" t="s">
+      <c r="A91" s="17" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A92" s="18" t="s">
+      <c r="A92" s="17" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="94" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A94" s="17" t="s">
+      <c r="A94" s="16" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A95" s="16"/>
+      <c r="A95" s="15"/>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A96" s="18" t="s">
+      <c r="A96" s="17" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A97" s="18" t="s">
+      <c r="A97" s="17" t="s">
         <v>132</v>
       </c>
     </row>
@@ -2205,9 +2208,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CACB33E-4510-4F0C-9DA0-AC4A31A9D7C3}">
-  <dimension ref="A1"/>
+  <dimension ref="B2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>